--- a/data-raw/metadata/butte_metadata.xlsx
+++ b/data-raw/metadata/butte_metadata.xlsx
@@ -1000,7 +1000,7 @@
         <v>35034</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46050</v>
+        <v>46118</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/metadata/butte_metadata.xlsx
+++ b/data-raw/metadata/butte_metadata.xlsx
@@ -1000,7 +1000,7 @@
         <v>35034</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46118</v>
+        <v>45979</v>
       </c>
     </row>
   </sheetData>
